--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8249-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8249-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA33FB12-0D9A-49C0-9C97-BDB8468C6668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4515217C-AE3B-4F45-BF77-C7F23615040D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7EEED957-4BF0-4BCA-A236-3C5E780DB534}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{62E43FFB-75A1-47A8-914E-D47A005E2AA7}"/>
   </bookViews>
   <sheets>
     <sheet name="8249-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1496,30 +1496,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF196C5-7CE8-4616-A9CF-69871775E807}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD44C5E7-FFD8-4923-BC46-5D7550E1CBB8}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1709,7 +1709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2023</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2021</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2020</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2019</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2018</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2017</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2016</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2015</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2014</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2013</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2012</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2011</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2010</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2009</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2008</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2007</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2006</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2005</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2004</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2003</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2002</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2001</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37" t="s">
         <v>53</v>
       </c>
